--- a/etf_holdings/2026-10-15_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-15_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,52 +439,52 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>00991A_異動類型</t>
+          <t>00981A_異動類型</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>00991A_調整方向</t>
+          <t>00981A_調整方向</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>00991A_股票名稱_昨日</t>
+          <t>00981A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>00991A_股票名稱_今日</t>
+          <t>00981A_股票名稱_今日</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>00991A_權重_昨日</t>
+          <t>00981A_權重_昨日</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>00991A_權重_今日</t>
+          <t>00981A_權重_今日</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>00991A_權重變化</t>
+          <t>00981A_權重變化</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>00991A_股數_昨日</t>
+          <t>00981A_股數_昨日</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>00991A_股數_今日</t>
+          <t>00981A_股數_今日</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>00991A_股數變化</t>
+          <t>00981A_股數變化</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
@@ -539,64 +539,64 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>00985A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>00985A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>00985A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>00985A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>00985A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>00985A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>00985A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>00985A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>00985A_股數變化</t>
+          <t>00407A_股數變化</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -604,65 +604,65 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00403A,00985A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+          <t>00407A,00981A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>6.26%</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5.40%</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-0.86%</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>1950000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-250,000</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.42%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>+0.19%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5423000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5808000</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>385,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>持續持有</t>
@@ -675,50 +675,50 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>80000</v>
+        <v>236000</v>
       </c>
       <c r="AG2" t="n">
-        <v>102000</v>
+        <v>306000</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>70,000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00985A,00991A</t>
+          <t>00403A,00981A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -741,218 +741,96 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>4.20%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>130000</v>
+        <v>6847000</v>
       </c>
       <c r="M3" t="n">
-        <v>150000</v>
+        <v>7046000</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+          <t>199,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>-0.46%</t>
-        </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>16000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>00985A,00991A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3.09%</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>+3.06%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>290000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>320000</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>30,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3.49%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>3.68%</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>+0.19%</t>
-        </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>119000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>134000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2.71%</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>2180000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>120,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
